--- a/cliente_banco_Tabajara.xlsx
+++ b/cliente_banco_Tabajara.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,15 +451,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Adenilson</t>
+          <t>aaa</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11122233366</v>
+        <v>1111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Poupanca</t>
+          <t>poup</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -475,15 +475,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>bbb</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>2222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pou</t>
+          <t>teset</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -493,6 +493,30 @@
         <v>401</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bbb</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>402</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/cliente_banco_Tabajara.xlsx
+++ b/cliente_banco_Tabajara.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,15 +451,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aaa</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1111</v>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>poup</t>
+          <t>Poupanca</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -469,54 +471,6 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bbb</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2222</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>teset</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>401</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bbb</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>402</v>
-      </c>
-      <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/cliente_banco_Tabajara.xlsx
+++ b/cliente_banco_Tabajara.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Poupanca</t>
+          <t>Corrente</t>
         </is>
       </c>
       <c r="D2" t="n">
